--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10号及11号 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8号及9号 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1198,7 +1061,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -3962,994 +3825,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>应天 - 10号及11号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>10 | 3022呎 (4+房)
-$38,077万
-$126,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (3房)
-$16,578万
-$77,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-$15,570万
-$71,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2153呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>10 | 2073呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>11 | 2112呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>应天 - 8号及9号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>8 | 2849呎 (4+房)
-$36,200万
-$127,062/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-$14,959万
-$70,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>8 | 1800呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>9 | 2056呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10号及11号" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8号及9号" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3825,4 +4005,994 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>10号及11号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>10 | 3022呎 (4+房)
+$38077万
+$126,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (3房)
+$16578万
+$77,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+$15570万
+$71,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2153呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>10 | 2073呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>11 | 2112呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8号及9号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>8 | 2849呎 (4+房)
+$36200万
+$127,062/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+$14959万
+$70,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1800呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>9 | 2056呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2153</v>
+        <v>2097</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>165781000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>77000</v>
+        <v>79056</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -2728,27 +2728,23 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>157069500</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>73500</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4225,9 +4221,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>10 | 2153呎 (3房)
+          <t>10 | 2097呎 (3房)
 $16578万
-$77,000/呎
+$79,056/呎
 (26年-07月)</t>
         </is>
       </c>
@@ -4563,7 +4559,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4573,7 +4569,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4703,12 +4699,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+$15707万
+$73,500/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -657,6 +657,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -714,6 +718,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -749,7 +773,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -760,6 +784,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -810,6 +854,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -860,6 +924,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -910,6 +994,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -960,6 +1064,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1010,6 +1134,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1060,6 +1204,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1110,6 +1274,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1160,6 +1344,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1206,6 +1410,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1252,6 +1476,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1302,6 +1546,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1352,6 +1616,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1686,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1452,6 +1756,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1502,6 +1826,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1552,6 +1896,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1602,6 +1966,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1652,6 +2036,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1702,6 +2106,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1752,6 +2176,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1802,6 +2246,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1852,6 +2316,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1902,6 +2386,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1952,6 +2456,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2002,6 +2526,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2052,6 +2596,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2102,6 +2666,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2152,6 +2736,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2202,6 +2806,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2252,6 +2876,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2302,6 +2946,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2352,6 +3016,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2398,6 +3082,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2448,6 +3152,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2498,6 +3222,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2548,6 +3292,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2598,6 +3362,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2648,6 +3432,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2698,6 +3502,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2744,6 +3568,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2794,6 +3638,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2829,7 +3693,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2840,6 +3704,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2890,6 +3774,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2940,6 +3844,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2990,6 +3914,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3040,6 +3984,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3090,6 +4054,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3140,6 +4124,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3190,6 +4194,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3240,6 +4264,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3290,6 +4334,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3340,6 +4404,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3390,6 +4474,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3440,6 +4544,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3490,6 +4614,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3540,6 +4684,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3590,6 +4754,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3640,6 +4824,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3690,6 +4894,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3740,6 +4964,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3790,6 +5034,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3840,6 +5104,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3890,6 +5174,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3940,6 +5244,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3990,13 +5314,33 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4116,7 +5460,7 @@
           <t>10 | 3022呎 (4+房)
 $38077万
 $126,000/呎
-(26年-06月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -4224,7 +5568,7 @@
           <t>10 | 2097呎 (3房)
 $16578万
 $79,056/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -4232,7 +5576,7 @@
           <t>11 | 2193呎 (4+房)
 $15570万
 $71,000/呎
-(26年-06月)</t>
+(26年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -4611,7 +5955,7 @@
           <t>8 | 2849呎 (4+房)
 $36200万
 $127,062/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -4704,7 +6048,7 @@
           <t>9 | 2137呎 (4+房)
 $15707万
 $73,500/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -4727,7 +6071,7 @@
           <t>9 | 2137呎 (4+房)
 $14959万
 $70,000/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3022</v>
+        <v>2955</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>380772000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>126000</v>
+        <v>128857</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -5457,9 +5457,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>10 | 3022呎 (4+房)
+          <t>10 | 2955呎 (4+房)
 $38077万
-$126,000/呎
+$128,857/呎
 (26年-07月-12日)</t>
         </is>
       </c>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2193</v>
+        <v>2133</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1399,14 +1399,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
         <v>155703000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>71000</v>
+        <v>72997</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -4034,23 +4034,19 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>126562500</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>67500</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4059,12 +4055,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4074,7 +4070,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5573,10 +5569,10 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>11 | 2193呎 (4+房)
+          <t>11 | 2133呎 (4+房)
 $15570万
-$71,000/呎
-(26年-06月-27日)</t>
+$72,997/呎
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5899,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5913,7 +5909,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6104,12 +6100,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
+$12656万
+$67,500/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -5456,7 +5456,7 @@
           <t>10 | 2955呎 (4+房)
 $38077万
 $128,857/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
           <t>10 | 2097呎 (3房)
 $16578万
 $79,056/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -5572,7 +5572,7 @@
           <t>11 | 2133呎 (4+房)
 $15570万
 $72,997/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
           <t>8 | 2849呎 (4+房)
 $36200万
 $127,062/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
           <t>9 | 2137呎 (4+房)
 $15707万
 $73,500/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
           <t>9 | 2137呎 (4+房)
 $14959万
 $70,000/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
           <t>8 | 1875呎 (3房)
 $12656万
 $67,500/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -5456,7 +5456,7 @@
           <t>10 | 2955呎 (4+房)
 $38077万
 $128,857/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
           <t>10 | 2097呎 (3房)
 $16578万
 $79,056/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -5572,7 +5572,7 @@
           <t>11 | 2133呎 (4+房)
 $15570万
 $72,997/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
           <t>8 | 2849呎 (4+房)
 $36200万
 $127,062/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
           <t>9 | 2137呎 (4+房)
 $15707万
 $73,500/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
           <t>9 | 2137呎 (4+房)
 $14959万
 $70,000/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
           <t>8 | 1875呎 (3房)
 $12656万
 $67,500/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
